--- a/Java24 NgoThanhBao Database Design.xlsx
+++ b/Java24 NgoThanhBao Database Design.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAF650B-7118-4CA3-82FF-07F560915913}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A6952F-AFF6-492C-B908-5BB7151F1D7C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="20160" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6180" yWindow="2160" windowWidth="20160" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1. Mô hình quan hệ" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,128 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+  <si>
+    <t>MatHang</t>
+  </si>
+  <si>
+    <t>MaMH</t>
+  </si>
+  <si>
+    <t>GiaBan</t>
+  </si>
+  <si>
+    <t>GiaMua</t>
+  </si>
+  <si>
+    <t>MauSac</t>
+  </si>
+  <si>
+    <t>HinhAnh(s)</t>
+  </si>
+  <si>
+    <t>MauSac(s)</t>
+  </si>
+  <si>
+    <t>ChatLieu(s)</t>
+  </si>
+  <si>
+    <t>KichThuoc(s)</t>
+  </si>
+  <si>
+    <t>DonHang</t>
+  </si>
+  <si>
+    <t>TenKhachHang</t>
+  </si>
+  <si>
+    <t>DiaChi</t>
+  </si>
+  <si>
+    <t>SDT</t>
+  </si>
+  <si>
+    <t>PTThanhToan</t>
+  </si>
+  <si>
+    <t>SoLuong</t>
+  </si>
+  <si>
+    <t>KhachHang</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>TKMangXaHoi</t>
+  </si>
+  <si>
+    <t>TrangThai</t>
+  </si>
+  <si>
+    <t>NVPhuTrach</t>
+  </si>
+  <si>
+    <t>NhanVien</t>
+  </si>
+  <si>
+    <t>TenNhanVien</t>
+  </si>
+  <si>
+    <t>MaNhanVien</t>
+  </si>
+  <si>
+    <t>MatKhau</t>
+  </si>
+  <si>
+    <t>ChiTietDon</t>
+  </si>
+  <si>
+    <t>ChuCuaHang</t>
+  </si>
+  <si>
+    <t>NgayDat</t>
+  </si>
+  <si>
+    <t>TongTien</t>
+  </si>
+  <si>
+    <t>PhiVanChuyen</t>
+  </si>
+  <si>
+    <t>GioHang</t>
+  </si>
+  <si>
+    <t>ChiTietMatHang</t>
+  </si>
+  <si>
+    <t>LoaiMH</t>
+  </si>
+  <si>
+    <t>TenChuCH</t>
+  </si>
+  <si>
+    <t>TaiKhoan</t>
+  </si>
+  <si>
+    <t>MaChuCH</t>
+  </si>
+  <si>
+    <t>ChucNangChu</t>
+  </si>
+  <si>
+    <t>ChucNangNV</t>
+  </si>
+  <si>
+    <t>MaDonHang</t>
+  </si>
+  <si>
+    <t>NgayTaoDon</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -38,7 +160,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +168,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -332,9 +470,386 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="C3:O20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="7" width="12.77734375" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.77734375" customWidth="1"/>
+    <col min="10" max="15" width="12.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+    </row>
+    <row r="4" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+    </row>
+    <row r="14" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+    </row>
+    <row r="15" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+    </row>
+    <row r="16" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
